--- a/testA.xlsx
+++ b/testA.xlsx
@@ -8,9 +8,8 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\itni\cs\py-study\study-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{453BB4BA-8237-4DD6-A7AE-E7C19CC866C7}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>최선희는 예쁘다</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -33,24 +32,27 @@
   <si>
     <t>황규석은 멋지다</t>
   </si>
+  <si>
+    <t>황은율은 예쁘다</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -81,7 +83,7 @@
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -94,7 +96,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -357,60 +359,60 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.95"/>
+  <sheetFormatPr defaultRowHeight="17.25"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" customWidth="1"/>
+    <col customWidth="true" max="1" min="1" width="20.6640625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.95">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.95">
+    <row r="2" spans="1:2">
       <c r="B2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.95">
+    <row r="3" spans="1:2">
       <c r="B3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.95">
+    <row r="4" spans="1:2">
       <c r="B4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.95">
+    <row r="5" spans="1:2">
       <c r="B5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.95">
+    <row r="6" spans="1:2">
       <c r="B6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.95">
+    <row r="7" spans="1:2">
       <c r="B7" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.95">
+    <row r="8" spans="1:2">
       <c r="B8" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.95">
+    <row r="9" spans="1:2">
       <c r="B9" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.95">
+    <row r="10" spans="1:2">
       <c r="B10" t="s">
         <v>1</v>
       </c>
@@ -418,6 +420,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup r:id="rId1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/testA.xlsx
+++ b/testA.xlsx
@@ -1,45 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23801"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\itni\cs\py-study\study-1\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="162913" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
-  <si>
-    <t>최선희는 예쁘다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>황규석은 멋지다</t>
-  </si>
-  <si>
-    <t>황은율은 예쁘다</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <name val="맑은 고딕"/>
@@ -58,7 +34,7 @@
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -77,21 +53,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -357,69 +392,94 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="17.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.25"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.6640625"/>
+    <col width="20.6640625" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="B3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="B4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="B5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="B6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="B7" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="B8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="B9" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="B10" t="s">
-        <v>1</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>황가달</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>황규석은 멋지다</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>황규석은 멋지다</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>황규석은 멋지다</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>황규석은 멋지다</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>황규석은 멋지다</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>황규석은 멋지다</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>황규석은 멋지다</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>황규석은 멋지다</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>황규석은 멋지다</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>황규석은 멋지다</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup r:id="rId1" orientation="portrait" paperSize="9"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>